--- a/Data/EXCEL/Transfer/salemon/202208/8465-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8465-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B013A74C-3784-4D6D-BBBF-41F14EC02CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DB6F8EE-3961-444C-AE4F-9F006EC33B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8465-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,25 +1227,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q98"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.125" customWidth="1"/>
-    <col min="2" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="10.375" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="9.5" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="9.875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="5" width="13.875" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="15.25" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="10" width="13.875" customWidth="1"/>
+    <col min="11" max="11" width="15.875" customWidth="1"/>
+    <col min="12" max="12" width="13.25" customWidth="1"/>
+    <col min="13" max="13" width="15.875" customWidth="1"/>
+    <col min="14" max="14" width="13.25" customWidth="1"/>
+    <col min="15" max="15" width="13.875" customWidth="1"/>
+    <col min="16" max="16" width="15.875" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1264,7 +1272,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1303,7 +1311,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1346,7 +1354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1385,7 +1393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1438,7 +1446,7 @@
         <v>-4.01</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1491,7 +1499,7 @@
         <v>-7.4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1544,7 +1552,7 @@
         <v>-6.7</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1597,7 +1605,7 @@
         <v>-2.31</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1650,7 +1658,7 @@
         <v>-0.68</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1703,7 +1711,7 @@
         <v>-4.18</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1756,7 +1764,7 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1809,7 +1817,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1862,7 +1870,7 @@
         <v>-11.7</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1915,7 +1923,7 @@
         <v>-14.4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1968,7 +1976,7 @@
         <v>-16.100000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2021,7 +2029,7 @@
         <v>-18.100000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2074,7 +2082,7 @@
         <v>-19.8</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2127,7 +2135,7 @@
         <v>-22.2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2180,7 +2188,7 @@
         <v>-25.8</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2233,7 +2241,7 @@
         <v>-29.7</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2286,7 +2294,7 @@
         <v>-36.299999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2339,7 +2347,7 @@
         <v>-43.4</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2392,7 +2400,7 @@
         <v>-50.4</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2445,7 +2453,7 @@
         <v>-68.900000000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2498,7 +2506,7 @@
         <v>-51.9</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2551,7 +2559,7 @@
         <v>-52.1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2604,7 +2612,7 @@
         <v>-51.9</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2657,7 +2665,7 @@
         <v>-51.6</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2710,7 +2718,7 @@
         <v>-49.5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2763,7 +2771,7 @@
         <v>-47.6</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2816,7 +2824,7 @@
         <v>-43.1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2869,7 +2877,7 @@
         <v>-39.799999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2922,7 +2930,7 @@
         <v>-28.9</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2975,7 +2983,7 @@
         <v>-20.5</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3028,7 +3036,7 @@
         <v>-25.6</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3081,7 +3089,7 @@
         <v>-5.48</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3134,7 +3142,7 @@
         <v>-7.57</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3187,7 +3195,7 @@
         <v>-6.19</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3240,7 +3248,7 @@
         <v>-8.86</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3293,7 +3301,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3346,7 +3354,7 @@
         <v>-16.600000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3399,7 +3407,7 @@
         <v>-20.2</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3452,7 +3460,7 @@
         <v>-26</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3505,7 +3513,7 @@
         <v>-29.8</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3558,7 +3566,7 @@
         <v>-37.299999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3611,7 +3619,7 @@
         <v>-42.5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3664,7 +3672,7 @@
         <v>-26.6</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3717,7 +3725,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3770,7 +3778,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3823,7 +3831,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3876,7 +3884,7 @@
         <v>39.299999999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3929,7 +3937,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3982,7 +3990,7 @@
         <v>62.3</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4035,7 +4043,7 @@
         <v>67.7</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4088,7 +4096,7 @@
         <v>74.7</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4141,7 +4149,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4194,7 +4202,7 @@
         <v>72.900000000000006</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4247,7 +4255,7 @@
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4300,7 +4308,7 @@
         <v>72.400000000000006</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4353,7 +4361,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4406,7 +4414,7 @@
         <v>-48.2</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4459,7 +4467,7 @@
         <v>-51.3</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4512,7 +4520,7 @@
         <v>-53.7</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4565,7 +4573,7 @@
         <v>-57.2</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4618,7 +4626,7 @@
         <v>-61.8</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4671,7 +4679,7 @@
         <v>-63.3</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4724,7 +4732,7 @@
         <v>-66.3</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4777,7 +4785,7 @@
         <v>-67.900000000000006</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4830,7 +4838,7 @@
         <v>-69.8</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4883,7 +4891,7 @@
         <v>-72</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4936,7 +4944,7 @@
         <v>-77</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4989,7 +4997,7 @@
         <v>-75.2</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5042,7 +5050,7 @@
         <v>-42.8</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5095,7 +5103,7 @@
         <v>-40.1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5148,7 +5156,7 @@
         <v>-38.700000000000003</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5201,7 +5209,7 @@
         <v>-36.799999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5254,7 +5262,7 @@
         <v>-34.299999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5307,7 +5315,7 @@
         <v>-30.4</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5360,7 +5368,7 @@
         <v>-28.3</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5413,7 +5421,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5466,7 +5474,7 @@
         <v>-30.2</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5519,7 +5527,7 @@
         <v>-32.299999999999997</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5572,7 +5580,7 @@
         <v>-17.8</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5625,7 +5633,7 @@
         <v>-25.8</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5678,7 +5686,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5731,7 +5739,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5784,7 +5792,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5837,7 +5845,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5890,7 +5898,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5943,7 +5951,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5996,7 +6004,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6049,7 +6057,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6102,7 +6110,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6155,7 +6163,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6208,7 +6216,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6261,7 +6269,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41913</v>
       </c>
@@ -6314,7 +6322,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41883</v>
       </c>
@@ -6382,7 +6390,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>